--- a/data/lineup-2025.xlsx
+++ b/data/lineup-2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pekkos/git/bingsjostamman.se/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pekkos/git/bingsjostamman.se/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00CB5FF-C4C1-0144-AF04-C9902F3124F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF95324-ECF2-8449-B7BF-2DE4B843F884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20940" yWindow="4660" windowWidth="28040" windowHeight="17440" xr2:uid="{60F76CC9-F7FE-B34D-9EF7-EFD856BA5ECF}"/>
+    <workbookView xWindow="67420" yWindow="10660" windowWidth="36000" windowHeight="21480" xr2:uid="{60F76CC9-F7FE-B34D-9EF7-EFD856BA5ECF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="93">
   <si>
     <t>day</t>
   </si>
@@ -47,9 +47,6 @@
     <t>description</t>
   </si>
   <si>
-    <t>url</t>
-  </si>
-  <si>
     <t>image</t>
   </si>
   <si>
@@ -77,67 +74,247 @@
     <t>Täby Spelmansgille</t>
   </si>
   <si>
+    <t>Täby Spelmansgille spelar polskor efter Peckos helmer</t>
+  </si>
+  <si>
+    <t>https://taby.se</t>
+  </si>
+  <si>
+    <t>Tunet</t>
+  </si>
+  <si>
+    <t>Kapellet</t>
+  </si>
+  <si>
+    <t>Nordanstigs spelmanslag</t>
+  </si>
+  <si>
+    <t>Malungs folkhögksola</t>
+  </si>
+  <si>
+    <t>Gamla och nya Malungselever hälsas välkomna att spela till dans</t>
+  </si>
+  <si>
+    <t>Bagarstugan</t>
+  </si>
+  <si>
+    <t>Dräktskick i Bingsjö</t>
+  </si>
+  <si>
+    <t>Se Bingsjödräkten i olika skepnader.</t>
+  </si>
+  <si>
+    <t>Tvallmusikinstrument</t>
+  </si>
+  <si>
+    <t>Träffa en byggare av vallmusikinstrument</t>
+  </si>
+  <si>
+    <t>Danislegården</t>
+  </si>
+  <si>
+    <t>Dalmålningar</t>
+  </si>
+  <si>
+    <t>Upplev de unika dalmålningarna av Winter Carl Hansson</t>
+  </si>
+  <si>
+    <t>Långdans och balladdans</t>
+  </si>
+  <si>
+    <t>Bystugebanan</t>
+  </si>
+  <si>
+    <t>Prova på polska</t>
+  </si>
+  <si>
+    <t>Levande ladan</t>
+  </si>
+  <si>
+    <t>Visstuga</t>
+  </si>
+  <si>
+    <t>Upplev en stunds stillhet med sångsektionen i Dalarnas Spelmansförbund.</t>
+  </si>
+  <si>
+    <t>Låttältet</t>
+  </si>
+  <si>
+    <t>Bingsjölåtar med Täby spelmansgille</t>
+  </si>
+  <si>
+    <t>Orelåtar med Ore spelmän</t>
+  </si>
+  <si>
+    <t>Norra Hälsingland med Nordanstigs spelmanslag</t>
+  </si>
+  <si>
+    <t>Rättvikslåtar med Rättviks spelmanslag</t>
+  </si>
+  <si>
+    <t>Södra Dalarna med Korsmora spelmän</t>
+  </si>
+  <si>
+    <t>Bröderna</t>
+  </si>
+  <si>
+    <t>Vallmusik: Jag lockar, jag kallar</t>
+  </si>
+  <si>
+    <t>Ethno</t>
+  </si>
+  <si>
+    <t>Årets Päkkos Gustaf-stipendiat</t>
+  </si>
+  <si>
+    <t>Halifax Rättvik Trio</t>
+  </si>
+  <si>
+    <t>Ola Bäckström</t>
+  </si>
+  <si>
+    <t>Kapell Malén</t>
+  </si>
+  <si>
+    <t>Sara Persson &amp; Lars Nordin</t>
+  </si>
+  <si>
+    <t>Eyra</t>
+  </si>
+  <si>
+    <t>Johanna Karlsson &amp; Ole Lindvall</t>
+  </si>
+  <si>
+    <t>Arvid Barnö Thuresson &amp; Daniela Söderlund</t>
+  </si>
+  <si>
+    <t>Logen</t>
+  </si>
+  <si>
+    <t>Mästarkursen</t>
+  </si>
+  <si>
+    <t>Dalarnas ungdomsspelmanslag</t>
+  </si>
+  <si>
+    <t>Ungtfolk på logen</t>
+  </si>
+  <si>
+    <t>Dragkroka</t>
+  </si>
+  <si>
+    <t>Thea Åslund &amp; Tove Lindberg</t>
+  </si>
+  <si>
+    <t>Täpp Ida Almlöf &amp; David Albertsson</t>
+  </si>
+  <si>
+    <t>Spelpiporna</t>
+  </si>
+  <si>
+    <t>BergRouDahl Trio</t>
+  </si>
+  <si>
+    <t>Patina</t>
+  </si>
+  <si>
+    <t>A&amp;O</t>
+  </si>
+  <si>
+    <t>Ellinor Fritz</t>
+  </si>
+  <si>
+    <t>Nygårdsgården</t>
+  </si>
+  <si>
+    <t>Spelmansmöte</t>
+  </si>
+  <si>
+    <t>Sofia Sandén och Ulrika Bodén träffas i årets spelmansmöte.</t>
+  </si>
+  <si>
+    <t>Dansbanan</t>
+  </si>
+  <si>
+    <t>Hoven Droven</t>
+  </si>
+  <si>
+    <t>Evigt unga Hoven Droven tar plats på scenen i invigningsprogrammet.</t>
+  </si>
+  <si>
+    <t>Ellika Frisell och Emma Reid</t>
+  </si>
+  <si>
+    <t>Låtar från Bingsjö med Ellika och Emma.</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>utställning</t>
+  </si>
+  <si>
+    <t>spela</t>
+  </si>
+  <si>
+    <t>dansa</t>
+  </si>
+  <si>
+    <t>lyssna</t>
+  </si>
+  <si>
+    <t>sjung</t>
+  </si>
+  <si>
+    <t>I årets spelmansmöte får rösten, den folkliga sången och särskilt musiken som klingat runt fäbodarna vara tongivande.</t>
+  </si>
+  <si>
+    <t>Första CD:n "Hia hia" släpptes år 1994 och sedan dess har generationer av spelmän älskat låtar som Köttpolska, Spoven, Bjekkergauken och Årepolskan.</t>
+  </si>
+  <si>
+    <t>Låtarna från Bingsjö och de traditionsbärare som spelat dem har lämnat ett djupt avtryck och blivit en av grundfärgerna i dessa fiolfantomers nyansrika och målande musikanteri.</t>
+  </si>
+  <si>
+    <t>Ulrika-Sofia_hgdace.jpg</t>
+  </si>
+  <si>
+    <t>HD_d0ttej.jpg</t>
+  </si>
+  <si>
+    <t>Ellika_Emma4012_lbpvwn.jpg</t>
+  </si>
+  <si>
+    <t>longdescription</t>
+  </si>
+  <si>
+    <t>placement</t>
+  </si>
+  <si>
+    <t>headline</t>
+  </si>
+  <si>
+    <t>Täby spelmansgille spelar Bingsjölåtar efter Reidar Hammarsten som under många år spelade ihop med Peckos Helmer</t>
+  </si>
+  <si>
+    <t>lattaltet_cidg9i</t>
+  </si>
+  <si>
+    <t>https://www.taby.se</t>
+  </si>
+  <si>
+    <t>https://ellika-emma.com</t>
+  </si>
+  <si>
+    <t>page</t>
+  </si>
+  <si>
+    <t>ref</t>
+  </si>
+  <si>
     <t>taby</t>
   </si>
   <si>
-    <t>Täby Spelmansgille spelar polskor efter Peckos helmer</t>
-  </si>
-  <si>
-    <t>https://taby.se</t>
-  </si>
-  <si>
-    <t>Malungs Folkhögskola</t>
-  </si>
-  <si>
-    <t>malung</t>
-  </si>
-  <si>
-    <t>Gamla och nya elever hälsas välkomna att spela till dans</t>
-  </si>
-  <si>
-    <t>https://malung.se</t>
-  </si>
-  <si>
-    <t>Tunet</t>
-  </si>
-  <si>
-    <t>Daniel Reid</t>
-  </si>
-  <si>
-    <t>daniel-reid</t>
-  </si>
-  <si>
-    <t>Daniel Reid spelar jättefint</t>
-  </si>
-  <si>
-    <t>Ann-Sofi Nilsson &amp; Agneta Stolpe</t>
-  </si>
-  <si>
-    <t>ann-sofi-agneta</t>
-  </si>
-  <si>
-    <t>Ann-Sofi och Agneta är supersamspelta, eller samsjungna.</t>
-  </si>
-  <si>
-    <t>htps://agnetastolpe.se</t>
-  </si>
-  <si>
-    <t>https://reid.se</t>
-  </si>
-  <si>
-    <t>Kapellet</t>
-  </si>
-  <si>
-    <t>Siri Ann Flensburg</t>
-  </si>
-  <si>
-    <t>siri-anna-flensburg</t>
-  </si>
-  <si>
-    <t>Sånger inspirerade av koralböcker</t>
-  </si>
-  <si>
-    <t>https://sirianna.se</t>
+    <t>artist</t>
   </si>
 </sst>
 </file>
@@ -185,10 +362,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -524,44 +705,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F23F1BC-D35E-3E42-8F88-5D61ED802479}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="3" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.5" customWidth="1"/>
+    <col min="8" max="8" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="43.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="L1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="2" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>5</v>
       </c>
       <c r="B2" s="2">
         <v>0.79166666666666663</v>
@@ -570,143 +772,953 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="K2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>91</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D16" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="E16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.84375</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.84375</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.86458333333333304</v>
+      </c>
+      <c r="D18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.86458333333333304</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.88541666666666596</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.88541666666666596</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.906249999999999</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.906249999999999</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.92708333333333304</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.92708333333333304</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.94791666666666596</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.94791666666666596</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.968750000000001</v>
+      </c>
+      <c r="D23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0.968750000000001</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.98958333333333504</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.98958333333333504</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1.0104166666666701</v>
+      </c>
+      <c r="D25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" t="s">
+        <v>74</v>
+      </c>
+      <c r="G25" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2">
+        <v>1.0104166666666701</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1.03125000000001</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="D27" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" t="s">
+        <v>73</v>
+      </c>
+      <c r="H27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D28" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="D29" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" t="s">
+        <v>73</v>
+      </c>
+      <c r="G29" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="D30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" t="s">
+        <v>92</v>
+      </c>
+      <c r="H30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="D31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" t="s">
+        <v>73</v>
+      </c>
+      <c r="G31" t="s">
+        <v>92</v>
+      </c>
+      <c r="H31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="D32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" t="s">
+        <v>73</v>
+      </c>
+      <c r="G32" t="s">
+        <v>92</v>
+      </c>
+      <c r="H32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0.937500000000001</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="D33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" t="s">
+        <v>73</v>
+      </c>
+      <c r="G33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.97916666666666696</v>
+      </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" t="s">
+        <v>73</v>
+      </c>
+      <c r="G34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H34" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0.97916666666666696</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" t="s">
+        <v>73</v>
+      </c>
+      <c r="G35" t="s">
+        <v>92</v>
+      </c>
+      <c r="H35" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="2">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" t="s">
+        <v>73</v>
+      </c>
+      <c r="G36" t="s">
+        <v>92</v>
+      </c>
+      <c r="H36" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="2">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="D37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" t="s">
+        <v>73</v>
+      </c>
+      <c r="G37" t="s">
+        <v>92</v>
+      </c>
+      <c r="H37" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" t="s">
+        <v>74</v>
+      </c>
+      <c r="F38" t="s">
+        <v>84</v>
+      </c>
+      <c r="G38" t="s">
+        <v>92</v>
+      </c>
+      <c r="H38" t="s">
+        <v>63</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="M38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="D39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" t="s">
+        <v>84</v>
+      </c>
+      <c r="G39" t="s">
+        <v>92</v>
+      </c>
+      <c r="H39" t="s">
+        <v>66</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="M39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="D40" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.875</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0.94791666666666663</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.96875</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H10" s="1"/>
+      <c r="E40" t="s">
+        <v>74</v>
+      </c>
+      <c r="F40" t="s">
+        <v>84</v>
+      </c>
+      <c r="G40" t="s">
+        <v>92</v>
+      </c>
+      <c r="H40" t="s">
+        <v>68</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M40" t="s">
+        <v>81</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{D7420A5C-DA5B-3E42-B6A8-AA5F100A7A61}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{803ED98F-E2C9-1144-BA70-50298876CB9F}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{74E60E93-7FDF-8546-BB9D-387FE5050746}"/>
-    <hyperlink ref="H6" r:id="rId4" xr:uid="{E630E115-A29A-FC47-A119-DCAEC6CB5C50}"/>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{D7420A5C-DA5B-3E42-B6A8-AA5F100A7A61}"/>
+    <hyperlink ref="K11" r:id="rId2" xr:uid="{C4FA8623-CFEA-BC46-9506-B032D834DE87}"/>
+    <hyperlink ref="K40" r:id="rId3" xr:uid="{83D448DB-1C05-9145-8045-C44B2965811A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/data/lineup-2025.xlsx
+++ b/data/lineup-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pekkos/git/bingsjostamman.se/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF95324-ECF2-8449-B7BF-2DE4B843F884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FB7CEB-45F3-8847-97E0-8D02117BBAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67420" yWindow="10660" windowWidth="36000" windowHeight="21480" xr2:uid="{60F76CC9-F7FE-B34D-9EF7-EFD856BA5ECF}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" xr2:uid="{60F76CC9-F7FE-B34D-9EF7-EFD856BA5ECF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="95">
   <si>
     <t>day</t>
   </si>
@@ -104,9 +104,6 @@
     <t>Se Bingsjödräkten i olika skepnader.</t>
   </si>
   <si>
-    <t>Tvallmusikinstrument</t>
-  </si>
-  <si>
     <t>Träffa en byggare av vallmusikinstrument</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>Långdans och balladdans</t>
   </si>
   <si>
-    <t>Bystugebanan</t>
-  </si>
-  <si>
     <t>Prova på polska</t>
   </si>
   <si>
@@ -140,18 +134,6 @@
     <t>Låttältet</t>
   </si>
   <si>
-    <t>Bingsjölåtar med Täby spelmansgille</t>
-  </si>
-  <si>
-    <t>Orelåtar med Ore spelmän</t>
-  </si>
-  <si>
-    <t>Norra Hälsingland med Nordanstigs spelmanslag</t>
-  </si>
-  <si>
-    <t>Rättvikslåtar med Rättviks spelmanslag</t>
-  </si>
-  <si>
     <t>Södra Dalarna med Korsmora spelmän</t>
   </si>
   <si>
@@ -315,6 +297,30 @@
   </si>
   <si>
     <t>artist</t>
+  </si>
+  <si>
+    <t>Vallmusikinstrument</t>
+  </si>
+  <si>
+    <t>Bingsjölåtar</t>
+  </si>
+  <si>
+    <t>Ore spelmän</t>
+  </si>
+  <si>
+    <t>Orelåtar</t>
+  </si>
+  <si>
+    <t>Låtar från södra Dalarna</t>
+  </si>
+  <si>
+    <t>Låtar från Norra Hälsingland</t>
+  </si>
+  <si>
+    <t>Rättvis spelmanslag</t>
+  </si>
+  <si>
+    <t>Rättvikslåtar</t>
   </si>
 </sst>
 </file>
@@ -734,19 +740,19 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" t="s">
         <v>83</v>
-      </c>
-      <c r="G1" t="s">
-        <v>89</v>
       </c>
       <c r="H1" t="s">
         <v>1</v>
       </c>
       <c r="I1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>2</v>
@@ -755,7 +761,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="M1" t="s">
         <v>3</v>
@@ -775,22 +781,25 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -807,10 +816,10 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
@@ -831,10 +840,10 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -858,7 +867,7 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H5" t="s">
         <v>20</v>
@@ -882,13 +891,13 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="K6" s="1"/>
     </row>
@@ -903,16 +912,16 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" t="s">
         <v>24</v>
       </c>
-      <c r="E7" t="s">
-        <v>71</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="J7" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="K7" s="1"/>
     </row>
@@ -930,10 +939,10 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K8" s="1"/>
     </row>
@@ -948,13 +957,13 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K9" s="1"/>
     </row>
@@ -969,16 +978,16 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="E10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="K10" s="1"/>
     </row>
@@ -993,28 +1002,31 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="I11" t="s">
-        <v>91</v>
+        <v>85</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1025,19 +1037,22 @@
         <v>0.875</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G12" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1048,19 +1063,22 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G13" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -1071,19 +1089,22 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -1094,16 +1115,19 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G15" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s">
-        <v>37</v>
+        <v>93</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
@@ -1120,13 +1144,13 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G16" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -1143,13 +1167,13 @@
         <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G17" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -1166,13 +1190,13 @@
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G18" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1189,10 +1213,10 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -1209,13 +1233,13 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G20" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -1232,13 +1256,13 @@
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G21" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -1255,13 +1279,13 @@
         <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G22" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -1278,13 +1302,13 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G23" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -1301,13 +1325,13 @@
         <v>14</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -1324,13 +1348,13 @@
         <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G25" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -1347,13 +1371,13 @@
         <v>14</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -1367,13 +1391,13 @@
         <v>0.8125</v>
       </c>
       <c r="D27" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H27" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -1387,16 +1411,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G28" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -1410,16 +1434,16 @@
         <v>0.875</v>
       </c>
       <c r="D29" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G29" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -1433,16 +1457,16 @@
         <v>0.89583333333333304</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G30" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -1456,16 +1480,16 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G31" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -1479,16 +1503,16 @@
         <v>0.9375</v>
       </c>
       <c r="D32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32" t="s">
+        <v>86</v>
+      </c>
+      <c r="H32" t="s">
         <v>50</v>
-      </c>
-      <c r="E32" t="s">
-        <v>73</v>
-      </c>
-      <c r="G32" t="s">
-        <v>92</v>
-      </c>
-      <c r="H32" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
@@ -1502,16 +1526,16 @@
         <v>0.95833333333333404</v>
       </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G33" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
@@ -1525,16 +1549,16 @@
         <v>0.97916666666666696</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E34" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G34" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
@@ -1548,16 +1572,16 @@
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E35" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G35" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
@@ -1571,16 +1595,16 @@
         <v>1.0208333333333299</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E36" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G36" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
@@ -1594,16 +1618,16 @@
         <v>1.0416666666666701</v>
       </c>
       <c r="D37" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E37" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G37" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -1617,28 +1641,28 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E38" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F38" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H38" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="M38" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -1652,28 +1676,28 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="D39" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E39" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39" t="s">
+        <v>78</v>
+      </c>
+      <c r="G39" t="s">
+        <v>86</v>
+      </c>
+      <c r="H39" t="s">
+        <v>60</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M39" t="s">
         <v>74</v>
-      </c>
-      <c r="F39" t="s">
-        <v>84</v>
-      </c>
-      <c r="G39" t="s">
-        <v>92</v>
-      </c>
-      <c r="H39" t="s">
-        <v>66</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="M39" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="68" x14ac:dyDescent="0.2">
@@ -1690,28 +1714,28 @@
         <v>15</v>
       </c>
       <c r="E40" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F40" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="M40" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
